--- a/data/trans_dic/IP16A112_2023R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 38,5</t>
+          <t>8,65; 39,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 49,22</t>
+          <t>12,37; 46,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 37,77</t>
+          <t>13,51; 36,91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 73,87</t>
+          <t>12,17; 73,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,29; 72,24</t>
+          <t>47,07; 71,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,95; 66,36</t>
+          <t>18,93; 66,82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 51,06</t>
+          <t>17,69; 50,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 29,23</t>
+          <t>3,02; 28,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,38; 33,6</t>
+          <t>12,6; 33,57</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,51; 73,08</t>
+          <t>25,3; 73,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,41; 88,52</t>
+          <t>34,63; 88,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,76; 77,0</t>
+          <t>39,0; 76,65</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,39; 73,85</t>
+          <t>25,11; 73,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,54; 64,08</t>
+          <t>15,37; 65,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,93; 61,06</t>
+          <t>26,28; 61,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 57,44</t>
+          <t>6,86; 55,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,33; 59,18</t>
+          <t>20,82; 61,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,28; 49,62</t>
+          <t>19,31; 51,18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,35; 72,48</t>
+          <t>44,65; 73,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,85; 59,39</t>
+          <t>29,47; 58,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,83; 61,5</t>
+          <t>38,63; 61,19</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,39; 71,5</t>
+          <t>18,47; 70,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 77,71</t>
+          <t>26,65; 76,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,26; 67,48</t>
+          <t>30,06; 64,61</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23,77; 49,62</t>
+          <t>24,25; 50,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37,26; 50,85</t>
+          <t>37,85; 51,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,87; 46,96</t>
+          <t>31,54; 47,59</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12678</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2627; 11956</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2760; 10409</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7121; 19455</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>25331</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28872</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7757; 47123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22668; 34556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21183; 74777</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8351</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3246; 9223</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>613; 5826</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4869; 12968</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6355</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7554</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13909</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3168; 9179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3835; 9767</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9201; 18085</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8657</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2204; 6438</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1721; 7315</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5249; 12237</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5247</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>527; 4242</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2833; 8426</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4110; 10894</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>17633</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>19437</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>37070</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>13300; 21878</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13069; 25741</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>28643; 45369</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9531</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1498; 5713</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>3119; 8919</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>5958; 12805</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>43497; 90425</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>69163; 93943</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>114202; 172312</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A112_2023R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 39,35</t>
+          <t>8,98; 39,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,37; 46,63</t>
+          <t>11,82; 48,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 36,91</t>
+          <t>14,29; 39,28</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,17; 73,93</t>
+          <t>12,44; 73,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,07; 71,75</t>
+          <t>47,9; 71,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 66,82</t>
+          <t>22,35; 66,84</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,69; 50,27</t>
+          <t>15,83; 50,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 28,72</t>
+          <t>3,71; 29,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,6; 33,57</t>
+          <t>12,5; 33,5</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,3; 73,31</t>
+          <t>23,69; 74,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,63; 88,2</t>
+          <t>36,65; 87,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,0; 76,65</t>
+          <t>39,2; 76,18</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 73,36</t>
+          <t>27,38; 74,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,37; 65,33</t>
+          <t>13,98; 65,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 61,27</t>
+          <t>26,81; 62,13</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 55,24</t>
+          <t>7,11; 57,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,82; 61,92</t>
+          <t>20,16; 60,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,31; 51,18</t>
+          <t>19,35; 50,16</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,65; 73,45</t>
+          <t>42,6; 72,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,47; 58,04</t>
+          <t>29,14; 59,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,63; 61,19</t>
+          <t>38,55; 60,68</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 70,41</t>
+          <t>18,8; 68,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,65; 76,19</t>
+          <t>29,71; 78,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,06; 64,61</t>
+          <t>30,7; 66,98</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24,25; 50,42</t>
+          <t>25,01; 50,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37,85; 51,42</t>
+          <t>37,19; 50,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,54; 47,59</t>
+          <t>32,59; 47,74</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2627; 11956</t>
+          <t>2728; 11853</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2760; 10409</t>
+          <t>2639; 10878</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7121; 19455</t>
+          <t>7534; 20702</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7757; 47123</t>
+          <t>7930; 47156</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22668; 34556</t>
+          <t>23071; 34663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21183; 74777</t>
+          <t>25013; 74794</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3246; 9223</t>
+          <t>2906; 9265</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>613; 5826</t>
+          <t>753; 6078</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4869; 12968</t>
+          <t>4830; 12943</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3168; 9179</t>
+          <t>2966; 9320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3835; 9767</t>
+          <t>4058; 9686</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9201; 18085</t>
+          <t>9249; 17974</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2204; 6438</t>
+          <t>2403; 6556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1721; 7315</t>
+          <t>1566; 7353</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5249; 12237</t>
+          <t>5354; 12410</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>527; 4242</t>
+          <t>546; 4426</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2833; 8426</t>
+          <t>2743; 8238</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4110; 10894</t>
+          <t>4119; 10677</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13300; 21878</t>
+          <t>12688; 21726</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13069; 25741</t>
+          <t>12923; 26309</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28643; 45369</t>
+          <t>28579; 44986</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1498; 5713</t>
+          <t>1526; 5560</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3119; 8919</t>
+          <t>3479; 9134</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5958; 12805</t>
+          <t>6084; 13275</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>43497; 90425</t>
+          <t>44851; 90132</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69163; 93943</t>
+          <t>67953; 92577</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>114202; 172312</t>
+          <t>118007; 172866</t>
         </is>
       </c>
     </row>
